--- a/jira_export_2026-08-28.xlsx
+++ b/jira_export_2026-08-28.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>522 h</t>
+          <t>527 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -905,14 +905,14 @@
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -928,7 +928,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="L6" s="15" t="inlineStr"/>
       <c r="M6" s="15" t="inlineStr"/>
@@ -3585,7 +3585,7 @@
         <v>2</v>
       </c>
       <c r="K40" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
@@ -6805,7 +6805,7 @@
         <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>138.825</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>19.83</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="86">
@@ -9415,7 +9415,7 @@
         <v>16</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
@@ -11378,7 +11378,7 @@
         <v>32101.087</v>
       </c>
       <c r="P153" s="19" t="n">
-        <v>134.31</v>
+        <v>131.97</v>
       </c>
     </row>
   </sheetData>
@@ -12235,16 +12235,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>176.75</v>
+        <v>178.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.75</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>13.75</v>
+        <v>16</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>223.25</v>
+        <v>227.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>76.25</v>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.7%</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>199</v>
+        <v>199.5</v>
       </c>
     </row>
   </sheetData>
@@ -13285,10 +13285,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -13306,7 +13306,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>9 clôture(s) : 8 projet(s), 1 rework</t>
+          <t>10 clôture(s) : 8 projet(s), 2 rework</t>
         </is>
       </c>
     </row>
@@ -13613,33 +13613,63 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>PDMDEP-4395</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>[COLMAR] LITTERALIS PRIME</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="inlineStr">
+        <is>
+          <t>COLMAR</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n">
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B16" s="29" t="n"/>
-      <c r="C16" s="29" t="n"/>
-      <c r="D16" s="29" t="n"/>
-      <c r="E16" s="29" t="n"/>
-      <c r="F16" s="29" t="n">
-        <v>1</v>
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="29" t="n"/>
+      <c r="F17" s="29" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-28.xlsx
+++ b/jira_export_2026-08-28.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>32,201 €</t>
+          <t>32,320 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,14 +772,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>14,093 €</t>
+          <t>14,104 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>18,108 €</t>
+          <t>18,216 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>556 h</t>
+          <t>562 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P155"/>
+  <dimension ref="A1:P156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3889,10 +3889,10 @@
         <v>0</v>
       </c>
       <c r="O44" s="16" t="n">
-        <v>438.2</v>
+        <v>449.155</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>44.94</v>
+        <v>46.07</v>
       </c>
     </row>
     <row r="45">
@@ -5185,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>323.7</v>
+        <v>431.6</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>1294.8</v>
+        <v>1726.4</v>
       </c>
     </row>
     <row r="63">
@@ -5953,7 +5953,7 @@
         <v>5</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>91</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>72.8</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="74">
@@ -7953,7 +7953,7 @@
         <v>9</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>9</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>9</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
@@ -8169,7 +8169,7 @@
         <v>9</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>13</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
@@ -10456,22 +10456,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15041</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD38 - ISERE] - Interface Itinisère - SAGT</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD38</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10494,25 +10494,17 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>26/04/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
         <v>28</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M138" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr"/>
+      <c r="M138" s="15" t="inlineStr"/>
       <c r="N138" s="16" t="n">
         <v>0</v>
       </c>
@@ -10526,22 +10518,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10564,17 +10556,25 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr"/>
-      <c r="M139" s="12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N139" s="13" t="n">
         <v>0</v>
       </c>
@@ -10588,22 +10588,22 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10626,14 +10626,14 @@
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L140" s="15" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -10650,12 +10650,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10683,19 +10683,19 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>33</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L141" s="12" t="inlineStr"/>
       <c r="M141" s="12" t="inlineStr"/>
@@ -10712,12 +10712,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10740,35 +10740,27 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L142" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M142" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L142" s="15" t="inlineStr"/>
+      <c r="M142" s="15" t="inlineStr"/>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
@@ -10782,22 +10774,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10810,23 +10802,35 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H143" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L143" s="12" t="inlineStr"/>
-      <c r="M143" s="12" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
@@ -10840,12 +10844,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10855,7 +10859,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10871,14 +10875,10 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H144" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H144" s="15" t="inlineStr"/>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
@@ -10887,16 +10887,8 @@
       <c r="K144" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="L144" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M144" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+      <c r="L144" s="15" t="inlineStr"/>
+      <c r="M144" s="15" t="inlineStr"/>
       <c r="N144" s="16" t="n">
         <v>0</v>
       </c>
@@ -10910,12 +10902,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -10925,7 +10917,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10948,17 +10940,25 @@
       </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr"/>
-      <c r="M145" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N145" s="13" t="n">
         <v>0</v>
       </c>
@@ -10972,28 +10972,26 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E146" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v/>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
@@ -11007,7 +11005,7 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
@@ -11019,7 +11017,7 @@
         <v>35</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L146" s="15" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -11036,23 +11034,27 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
@@ -11067,19 +11069,19 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>9</v>
+        <v>1.25</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11096,27 +11098,23 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C148" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr"/>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E148" s="15" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F148" s="15" t="inlineStr">
@@ -11131,19 +11129,19 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11160,21 +11158,29 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C149" s="12" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11182,17 +11188,21 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K149" s="12" t="n">
         <v>0.5</v>
@@ -11212,18 +11222,18 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr"/>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E150" s="15" t="inlineStr"/>
@@ -11240,14 +11250,14 @@
       <c r="H150" s="15" t="inlineStr"/>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11264,18 +11274,18 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PSC-1315</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr"/>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE RANG DU FLIERS</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr"/>
@@ -11286,36 +11296,28 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr"/>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34778</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>00172868</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O151" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P151" s="13" t="n">
         <v>0</v>
@@ -11324,18 +11326,18 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1315</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr"/>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE RANG DU FLIERS</t>
         </is>
       </c>
       <c r="E152" s="15" t="inlineStr"/>
@@ -11352,50 +11354,50 @@
       <c r="H152" s="15" t="inlineStr"/>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34778</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00172868</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O152" s="16" t="n">
-        <v>595.7</v>
+        <v>100</v>
       </c>
       <c r="P152" s="16" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr"/>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr"/>
@@ -11406,48 +11408,56 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr"/>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr"/>
-      <c r="M153" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O153" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P153" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr"/>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E154" s="15" t="inlineStr"/>
@@ -11464,11 +11474,11 @@
       <c r="H154" s="15" t="inlineStr"/>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K154" s="15" t="n">
         <v>0.25</v>
@@ -11486,31 +11496,83 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="18" t="inlineStr">
+      <c r="A155" s="11" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B155" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr"/>
+      <c r="D155" s="12" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E155" s="12" t="inlineStr"/>
+      <c r="F155" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr"/>
+      <c r="I155" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J155" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K155" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr"/>
+      <c r="M155" s="12" t="inlineStr"/>
+      <c r="N155" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B155" s="18" t="inlineStr"/>
-      <c r="C155" s="18" t="inlineStr"/>
-      <c r="D155" s="18" t="inlineStr"/>
-      <c r="E155" s="18" t="inlineStr"/>
-      <c r="F155" s="18" t="inlineStr"/>
-      <c r="G155" s="18" t="inlineStr"/>
-      <c r="H155" s="18" t="inlineStr"/>
-      <c r="I155" s="18" t="inlineStr"/>
-      <c r="J155" s="18" t="inlineStr"/>
-      <c r="K155" s="18" t="inlineStr"/>
-      <c r="L155" s="18" t="inlineStr"/>
-      <c r="M155" s="18" t="inlineStr"/>
-      <c r="N155" s="19" t="n">
+      <c r="B156" s="18" t="inlineStr"/>
+      <c r="C156" s="18" t="inlineStr"/>
+      <c r="D156" s="18" t="inlineStr"/>
+      <c r="E156" s="18" t="inlineStr"/>
+      <c r="F156" s="18" t="inlineStr"/>
+      <c r="G156" s="18" t="inlineStr"/>
+      <c r="H156" s="18" t="inlineStr"/>
+      <c r="I156" s="18" t="inlineStr"/>
+      <c r="J156" s="18" t="inlineStr"/>
+      <c r="K156" s="18" t="inlineStr"/>
+      <c r="L156" s="18" t="inlineStr"/>
+      <c r="M156" s="18" t="inlineStr"/>
+      <c r="N156" s="19" t="n">
         <v>54889.395</v>
       </c>
-      <c r="O155" s="19" t="n">
-        <v>32201.087</v>
-      </c>
-      <c r="P155" s="19" t="n">
-        <v>128.93</v>
+      <c r="O156" s="19" t="n">
+        <v>32319.942</v>
+      </c>
+      <c r="P156" s="19" t="n">
+        <v>127.12</v>
       </c>
     </row>
   </sheetData>
@@ -11666,6 +11728,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12369,16 +12432,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>183.25</v>
+        <v>186.5</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>34.75</v>
+        <v>36</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>16</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>234</v>
+        <v>238.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>84.5</v>
@@ -12388,7 +12451,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12493,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>212.5</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -12515,10 +12578,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>367973</v>
+        <v>367854</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>137626</v>
+        <v>137507</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>230347</v>
@@ -12540,10 +12603,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>165789</v>
+        <v>165778</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>61688</v>
+        <v>61678</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104101</v>
@@ -12565,10 +12628,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>202184</v>
+        <v>202076</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>75937</v>
+        <v>75829</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>126247</v>
